--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_372_R38.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_372_R38.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7853</v>
+        <v>3.7066</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3754</v>
+        <v>1.1958</v>
       </c>
       <c r="F2" t="n">
-        <v>2.41</v>
+        <v>2.5108</v>
       </c>
       <c r="G2" t="n">
         <v>2.1321</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>1.813</v>
+        <v>0.7343</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6869</v>
+        <v>0.5074</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1261</v>
+        <v>0.2269</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9954</v>
+        <v>3.6181</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3464</v>
+        <v>4.7002</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.351</v>
+        <v>-1.0821</v>
       </c>
       <c r="G3" t="n">
         <v>0.1583</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0394</v>
+        <v>-0.4167</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8962</v>
+        <v>-0.5423</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1432</v>
+        <v>0.1256</v>
       </c>
       <c r="V3" t="n">
         <v>4.5724</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1618</v>
+        <v>1.7306</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8332000000000001</v>
+        <v>1.9118</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3287</v>
+        <v>-0.1812</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4315</v>
+        <v>-0.1188</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2341</v>
+        <v>0.8548</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1975</v>
+        <v>-0.9736</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.1449</v>
+        <v>2.4512</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1611</v>
+        <v>1.9494</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.9838</v>
+        <v>0.5018</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2866</v>
+        <v>-2.57</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.073</v>
+        <v>-1.0945</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7863</v>
+        <v>-1.4755</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8279</v>
+        <v>-0.2407</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8363</v>
+        <v>-0.4518</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0083</v>
+        <v>0.2111</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1418</v>
+        <v>0.9304</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5448</v>
+        <v>1.2176</v>
       </c>
       <c r="E5" t="n">
-        <v>1.558</v>
+        <v>-0.3464</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0132</v>
+        <v>1.5639</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1188</v>
+        <v>-1.4315</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8548</v>
+        <v>-1.2341</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9736</v>
+        <v>-0.1975</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4512</v>
+        <v>-1.1449</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9494</v>
+        <v>-0.1611</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5018</v>
+        <v>-0.9838</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.57</v>
+        <v>-0.2866</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0945</v>
+        <v>-1.073</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4755</v>
+        <v>0.7863</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4266</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8057</v>
+        <v>0.6567</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3791</v>
+        <v>0.2269</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9304</v>
+        <v>0.1418</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.006</v>
+        <v>0.5331</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7641</v>
+        <v>-0.2923</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7581</v>
+        <v>0.8253</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2288</v>
@@ -922,13 +922,13 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.4424</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3576</v>
+        <v>0.1142</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2609</v>
+        <v>0.3282</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5361</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.244</v>
+        <v>0.1606</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0668</v>
+        <v>0.405</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1772</v>
+        <v>-0.2444</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6037</v>
@@ -1000,13 +1000,13 @@
         <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1125</v>
+        <v>0.5171</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4323</v>
+        <v>0.0395</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5447</v>
+        <v>0.4775</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0722</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>T. BLATT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.735</v>
+        <v>-1.2271</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5254</v>
+        <v>-1.7744</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7904</v>
+        <v>0.5473</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9171</v>
+        <v>-0.545</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2652</v>
+        <v>0.4455</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3481</v>
+        <v>-0.9905</v>
       </c>
       <c r="J8" t="n">
-        <v>0.128</v>
+        <v>1.057</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6449</v>
+        <v>2.2015</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7729</v>
+        <v>-1.1445</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0451</v>
+        <v>-1.602</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6203</v>
+        <v>-1.756</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4248</v>
+        <v>0.154</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R8" t="n">
         <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6281</v>
+        <v>-0.3626</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3339</v>
+        <v>-0.4244</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9619</v>
+        <v>0.0617</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. BLATT</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7998</v>
+        <v>-2.9956</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2463</v>
+        <v>-2.6434</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4465</v>
+        <v>-0.3522</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.545</v>
+        <v>-1.9171</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4455</v>
+        <v>-2.2652</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9905</v>
+        <v>0.3481</v>
       </c>
       <c r="J9" t="n">
-        <v>1.057</v>
+        <v>0.128</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2015</v>
+        <v>-0.6449</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1445</v>
+        <v>0.7729</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.602</v>
+        <v>-2.0451</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.756</v>
+        <v>-1.6203</v>
       </c>
       <c r="O9" t="n">
-        <v>0.154</v>
+        <v>-0.4248</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
         <v>2.0876</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9353</v>
+        <v>0.3675</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8962</v>
+        <v>-0.4518</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0391</v>
+        <v>0.8193</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1543</v>
+        <v>-5.1214</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.427</v>
+        <v>-2.6629</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7273</v>
+        <v>-2.4585</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8988</v>
@@ -1234,13 +1234,13 @@
         <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0958</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2047</v>
+        <v>-0.0312</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3005</v>
+        <v>-0.0316</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6203</v>
+        <v>-5.6944</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1755</v>
+        <v>-4.5857</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4448</v>
+        <v>-1.1087</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2523</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.136</v>
+        <v>-0.2102</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.731</v>
+        <v>-0.1412</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.405</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0721</v>
+        <v>-4.0719</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0921</v>
+        <v>-4.0923</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02020000000000022</v>
+        <v>0.02019999999999977</v>
       </c>
       <c r="G12" t="n">
         <v>-9.705599999999999</v>
@@ -1390,10 +1390,10 @@
         <v>19.716</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6518</v>
+        <v>1.6519</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7249999999999996</v>
+        <v>-0.7249</v>
       </c>
       <c r="U12" t="n">
         <v>2.3766</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8092</v>
+        <v>4.2595</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3559</v>
+        <v>1.8277</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4533</v>
+        <v>2.4318</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1538</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1924</v>
+        <v>0.6427</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6642</v>
+        <v>-0.1924</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8566</v>
+        <v>0.8351</v>
       </c>
       <c r="V13" t="n">
         <v>4.147</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1002</v>
+        <v>3.6336</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3099</v>
+        <v>2.4279</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7903</v>
+        <v>1.2057</v>
       </c>
       <c r="G14" t="n">
         <v>3.1697</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7859</v>
+        <v>-0.2526</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1885</v>
+        <v>0.2269</v>
       </c>
       <c r="V14" t="n">
         <v>0.2525</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>F. FERRARI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8744</v>
+        <v>2.4748</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7006</v>
+        <v>2.1035</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1739</v>
+        <v>0.3714</v>
       </c>
       <c r="G15" t="n">
-        <v>4.5728</v>
+        <v>0.7673</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9963</v>
+        <v>0.4227</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5765</v>
+        <v>0.3447</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5909</v>
+        <v>0.5854</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2722</v>
+        <v>0.7093</v>
       </c>
       <c r="L15" t="n">
-        <v>2.3187</v>
+        <v>-0.1239</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0181</v>
+        <v>0.1819</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2759</v>
+        <v>-0.2866</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2578</v>
+        <v>0.4685</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.7834</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.871</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0851</v>
+        <v>0.0116</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9085</v>
+        <v>0.1417</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1766</v>
+        <v>-0.13</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="X15" t="n">
         <v>-1.0722</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.299</v>
+        <v>2.1667</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2106</v>
+        <v>0.9929</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0883</v>
+        <v>1.1739</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3688</v>
+        <v>4.5728</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7836</v>
+        <v>1.9963</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4148</v>
+        <v>2.5765</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9334</v>
+        <v>4.5909</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7126</v>
+        <v>2.2722</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2208</v>
+        <v>2.3187</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5646</v>
+        <v>-0.0181</v>
       </c>
       <c r="N16" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.2759</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.2578</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.232</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.5515</v>
+        <v>-4.871</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7008</v>
+        <v>0.3774</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6869</v>
+        <v>0.2008</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0139</v>
+        <v>0.1766</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.5387</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8818</v>
+        <v>1.8774</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5645</v>
+        <v>0.6824</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3174</v>
+        <v>1.195</v>
       </c>
       <c r="G17" t="n">
         <v>3.7746</v>
@@ -1780,13 +1780,13 @@
         <v>2.5515</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5706</v>
+        <v>-0.575</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8883</v>
+        <v>-0.7703</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3176</v>
+        <v>0.1953</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3943</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. FERRARI</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7507</v>
+        <v>0.6654</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5137</v>
+        <v>0.9132</v>
       </c>
       <c r="F18" t="n">
-        <v>0.237</v>
+        <v>-0.2477</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7673</v>
+        <v>2.3688</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4227</v>
+        <v>2.7836</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3447</v>
+        <v>-0.4148</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5854</v>
+        <v>2.9334</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7093</v>
+        <v>2.7126</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1239</v>
+        <v>0.2208</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1819</v>
+        <v>-0.5646</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2866</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4685</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7125</v>
+        <v>1.0673</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4481</v>
+        <v>0.3894</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2645</v>
+        <v>0.6778</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5361</v>
+        <v>-2.5387</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6083</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="19">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9657</v>
+        <v>-1.2643</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5781</v>
+        <v>-2.4602</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6125</v>
+        <v>1.1959</v>
       </c>
       <c r="G20" t="n">
         <v>0.3987</v>
@@ -2014,13 +2014,13 @@
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4365</v>
+        <v>-0.7352</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6721</v>
+        <v>-0.5542</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7644</v>
+        <v>-0.181</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0988</v>
+        <v>-1.8972</v>
       </c>
       <c r="E21" t="n">
         <v>-1.2478</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.851</v>
+        <v>-0.6494</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9528</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5377</v>
+        <v>-0.3361</v>
       </c>
       <c r="T21" t="n">
         <v>-0.5149</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0228</v>
+        <v>0.1788</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6836</v>
+        <v>-2.7578</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2625</v>
+        <v>-2.6727</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4211</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3611</v>
@@ -2170,13 +2170,13 @@
         <v>2.0876</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2502</v>
+        <v>-0.3244</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7468</v>
+        <v>-0.1571</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5034</v>
+        <v>-0.1674</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6083</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7274</v>
+        <v>-3.3457</v>
       </c>
       <c r="E23" t="n">
         <v>-2.9814</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.746</v>
+        <v>-0.3643</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7104</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3365</v>
+        <v>0.0452</v>
       </c>
       <c r="T23" t="n">
         <v>-0.4402</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1037</v>
+        <v>0.4854</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1444</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.071799999999998</v>
+        <v>5.644400000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4146000000000001</v>
+        <v>-0.4144999999999985</v>
       </c>
       <c r="F24" t="n">
-        <v>4.486599999999999</v>
+        <v>6.0593</v>
       </c>
       <c r="G24" t="n">
         <v>9.7058</v>
@@ -2326,19 +2326,19 @@
         <v>18.5563</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.651600000000001</v>
+        <v>-0.07909999999999992</v>
       </c>
       <c r="T24" t="n">
         <v>-2.3767</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7248000000000001</v>
+        <v>2.2975</v>
       </c>
       <c r="V24" t="n">
         <v>-2.822299999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>7.394699999999999</v>
+        <v>7.3947</v>
       </c>
       <c r="X24" t="n">
         <v>-10.217</v>
